--- a/data/trans_orig/IP07A20-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A20-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con sus profesores en 2007 (tasa de respuesta: 99,0%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el adulto en 2007 (tasa de respuesta: 99,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57218</t>
+          <t>56898</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75327</t>
+          <t>75472</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44548</t>
+          <t>45587</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63280</t>
+          <t>64123</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>108079</t>
+          <t>106607</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>134620</t>
+          <t>133167</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>49,89%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40496</t>
+          <t>40598</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58524</t>
+          <t>59295</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57856</t>
+          <t>57756</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77136</t>
+          <t>75621</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>103624</t>
+          <t>103678</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>129743</t>
+          <t>130569</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,91%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4152</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13565</t>
+          <t>13265</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11229</t>
+          <t>11159</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22699</t>
+          <t>23180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17132</t>
+          <t>18097</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33707</t>
+          <t>32979</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7520</t>
+          <t>7085</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>620</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2366</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9963</t>
+          <t>9603</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67984</t>
+          <t>65542</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>89418</t>
+          <t>89510</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60410</t>
+          <t>61606</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82787</t>
+          <t>82733</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>134867</t>
+          <t>135901</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>165502</t>
+          <t>168084</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,53%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78035</t>
+          <t>77925</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>100377</t>
+          <t>100207</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>82896</t>
+          <t>83014</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>105602</t>
+          <t>105892</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>167229</t>
+          <t>166653</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>198313</t>
+          <t>198129</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,13%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13246</t>
+          <t>12777</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26566</t>
+          <t>26530</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20673</t>
+          <t>20999</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36420</t>
+          <t>37501</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>37243</t>
+          <t>37642</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>57757</t>
+          <t>57529</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6610</t>
+          <t>6849</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12257</t>
+          <t>12562</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16299</t>
+          <t>16319</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7346</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9523</t>
+          <t>9264</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>130357</t>
+          <t>128755</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>157741</t>
+          <t>158587</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>112237</t>
+          <t>113696</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>141656</t>
+          <t>142355</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>250338</t>
+          <t>248371</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>292281</t>
+          <t>290182</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,82%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124910</t>
+          <t>125097</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>152441</t>
+          <t>154385</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>145249</t>
+          <t>146029</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>175793</t>
+          <t>175146</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>278823</t>
+          <t>280819</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>320449</t>
+          <t>320318</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,38%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19490</t>
+          <t>19229</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>36033</t>
+          <t>35707</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>34758</t>
+          <t>35781</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55043</t>
+          <t>55196</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>59229</t>
+          <t>60014</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>84981</t>
+          <t>85292</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2757</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10782</t>
+          <t>11158</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5050</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15972</t>
+          <t>15487</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10142</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23038</t>
+          <t>23029</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7125</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,39 +2563,39 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4175</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>4162</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8590</t>
+          <t>9069</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con sus profesores en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>86903</t>
+          <t>88520</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>107499</t>
+          <t>107053</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>82200</t>
+          <t>83968</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>103688</t>
+          <t>104571</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>178344</t>
+          <t>177560</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>205207</t>
+          <t>206161</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>66,18%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41719</t>
+          <t>41306</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61697</t>
+          <t>59781</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40924</t>
+          <t>40226</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59691</t>
+          <t>59379</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>87244</t>
+          <t>87153</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113343</t>
+          <t>114315</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,69%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>2860</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12780</t>
+          <t>11603</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12832</t>
+          <t>12635</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8560</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21123</t>
+          <t>21000</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>6472</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7638</t>
+          <t>8668</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>678</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5373</t>
+          <t>5856</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>679</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>5724</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82521</t>
+          <t>82040</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>103637</t>
+          <t>102912</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>86832</t>
+          <t>85523</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108500</t>
+          <t>106543</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>175833</t>
+          <t>175596</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>205619</t>
+          <t>204833</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>59,96%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46484</t>
+          <t>46345</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67225</t>
+          <t>66171</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50151</t>
+          <t>50152</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70440</t>
+          <t>69939</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>101386</t>
+          <t>101281</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>130399</t>
+          <t>130021</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,06%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20002</t>
+          <t>20088</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8295</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19867</t>
+          <t>19882</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18926</t>
+          <t>19216</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34957</t>
+          <t>35359</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>6704</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>7968</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12969</t>
+          <t>12225</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>602</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>564</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>4781</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8045</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>175024</t>
+          <t>174466</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>203519</t>
+          <t>204506</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>176634</t>
+          <t>177438</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>205886</t>
+          <t>206376</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>358713</t>
+          <t>362196</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>402789</t>
+          <t>401932</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,54%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92578</t>
+          <t>92885</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>121803</t>
+          <t>122301</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95099</t>
+          <t>94866</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124089</t>
+          <t>124125</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>196080</t>
+          <t>196475</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>236945</t>
+          <t>233712</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>35,78%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13140</t>
+          <t>13759</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27813</t>
+          <t>28272</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14074</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28972</t>
+          <t>28313</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>30149</t>
+          <t>30710</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>51007</t>
+          <t>51591</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11449</t>
+          <t>12275</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>5256</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15845</t>
+          <t>16144</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10685</t>
+          <t>10708</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con sus profesores en 2016 (tasa de respuesta: 98,52%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el adulto en 2016 (tasa de respuesta: 98,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>94492</t>
+          <t>93753</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>116875</t>
+          <t>116564</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>95391</t>
+          <t>96495</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>117250</t>
+          <t>117728</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>195840</t>
+          <t>195405</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>227707</t>
+          <t>228339</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,52%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58980</t>
+          <t>58701</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79640</t>
+          <t>80974</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53232</t>
+          <t>53479</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75118</t>
+          <t>73653</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117714</t>
+          <t>117672</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>149427</t>
+          <t>149497</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,28%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5683</t>
+          <t>6042</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16376</t>
+          <t>16133</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6397</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17489</t>
+          <t>17308</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14354</t>
+          <t>14493</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29265</t>
+          <t>29480</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>584</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>5638</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3566</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>691</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6823</t>
+          <t>6253</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8115</t>
+          <t>7490</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71972</t>
+          <t>71355</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>93723</t>
+          <t>92809</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72102</t>
+          <t>72695</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94377</t>
+          <t>94815</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>150024</t>
+          <t>148040</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>180395</t>
+          <t>179886</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,39%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54875</t>
+          <t>55349</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>76198</t>
+          <t>75640</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56662</t>
+          <t>56312</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78528</t>
+          <t>78480</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>117031</t>
+          <t>118141</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>147451</t>
+          <t>148941</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>43,38%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14763</t>
+          <t>14517</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28826</t>
+          <t>29055</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12705</t>
+          <t>12580</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27046</t>
+          <t>26031</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30797</t>
+          <t>30546</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>50821</t>
+          <t>49568</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>3933</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7711</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>8659</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5427</t>
+          <t>4974</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3629</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>5865</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>172509</t>
+          <t>172687</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>205403</t>
+          <t>204699</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>173476</t>
+          <t>173853</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>203966</t>
+          <t>204992</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>356455</t>
+          <t>354578</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>400078</t>
+          <t>402416</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>56,32%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>118373</t>
+          <t>116979</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>148833</t>
+          <t>148668</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>116070</t>
+          <t>116458</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>147393</t>
+          <t>146823</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>243987</t>
+          <t>244320</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>286054</t>
+          <t>288686</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,4%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23636</t>
+          <t>22959</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>40761</t>
+          <t>39371</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22118</t>
+          <t>21012</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40641</t>
+          <t>38879</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>49672</t>
+          <t>49835</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74192</t>
+          <t>72745</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>2167</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9813</t>
+          <t>10337</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3021</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11450</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -7105,7 +7105,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>7684</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07A20-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A20-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el adulto en 2007 (tasa de respuesta: 99,0%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el/la adulto/a [KIDSCREEN 20] en 2007 (tasa de respuesta: 99,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>54382</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>44529</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>63466</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>38,84%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>31,8%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>45,33%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>66138</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>56898</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>75472</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>57390</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>75310</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>52,11%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>44,83%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>59,47%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>54382</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>45587</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>64123</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>38,84%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>106607</t>
+          <t>105160</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133167</t>
+          <t>132569</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,66%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>66819</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>57614</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>76583</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>47,72%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>41,15%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>54,69%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>49706</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>40598</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>59295</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>58644</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>39,16%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>31,99%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>46,72%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>66819</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>57756</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>75621</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>47,72%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>103678</t>
+          <t>104723</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>130569</t>
+          <t>130713</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,97%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16685</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11097</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>23426</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11,92%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>7,93%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>16,73%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>8020</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4207</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13265</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>4517</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>13666</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>6,32%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>10,45%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>16685</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>11159</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>23180</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>11,92%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18097</t>
+          <t>18069</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32979</t>
+          <t>33733</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2133</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6392</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,57%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3052</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1095</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7085</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1088</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6370</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,4%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,86%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2133</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6125</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>2426</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>9940</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>140019</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>140019</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>140019</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>126916</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>126916</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>126916</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>140019</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>140019</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>140019</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>72324</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>62407</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>82958</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>35,58%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>30,7%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>40,81%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>77729</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>65542</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>89510</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>68080</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>88514</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>40,5%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>34,15%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>46,64%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>72324</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>61606</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>82733</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>35,58%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>135901</t>
+          <t>134499</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>168084</t>
+          <t>166329</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,09%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>94242</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>83589</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>104922</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>46,36%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>41,12%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>51,62%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>89101</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>77925</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>100207</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>78798</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>100196</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>46,42%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>40,6%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>52,21%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>94242</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>83014</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>105892</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>46,36%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>166653</t>
+          <t>167317</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>198129</t>
+          <t>200569</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,75%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>28071</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>20971</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>36437</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>13,81%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>10,32%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>17,93%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>18984</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>12777</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>26530</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>12931</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>26623</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>9,89%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,66%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>13,82%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>28071</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>20999</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>37501</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>13,81%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>37642</t>
+          <t>37471</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>57529</t>
+          <t>57053</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7270</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3808</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12529</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,16%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2857</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>746</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6849</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>712</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7152</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,49%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>7270</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3922</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>12562</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16319</t>
+          <t>16399</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -1856,72 +1856,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4825</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>3266</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1246</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7197</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1245</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>7665</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,7%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4777</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9264</t>
+          <t>9088</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>203271</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>203271</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>203271</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>283</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>191937</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>191937</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>191937</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>203271</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>203271</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>203271</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>126706</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>112293</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>139990</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>36,91%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>32,71%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>40,78%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>143867</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>128755</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>158587</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>129108</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>157774</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>45,12%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>40,38%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>49,74%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>126706</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>113696</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>142355</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>36,91%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>248371</t>
+          <t>248353</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>290182</t>
+          <t>291460</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>44,02%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>161061</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>146878</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>175755</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>46,92%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>42,79%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>51,2%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>138807</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>125097</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>154385</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>125415</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>153784</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>43,53%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>39,23%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>48,42%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>161061</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>146029</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>175146</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>46,92%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>280819</t>
+          <t>280219</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>320318</t>
+          <t>322118</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,65%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>44755</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>35560</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>55827</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>13,04%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>10,36%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>16,26%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>27004</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>19229</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>35707</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>19195</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>36029</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>8,47%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>11,2%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>44755</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>35781</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>55196</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>13,04%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>60014</t>
+          <t>60012</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>85292</t>
+          <t>84487</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>9403</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>15146</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4,41%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>5909</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2853</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>11158</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2679</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>10909</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,85%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>9403</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>5050</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>15487</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9902</t>
+          <t>10288</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23029</t>
+          <t>22310</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -2538,74 +2538,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>3266</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1258</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7243</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1278</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>7236</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>1,02%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>2,27%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>4175</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>7</t>
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9069</t>
+          <t>9869</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>343289</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>343289</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>343289</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>473</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>318853</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>318853</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>318853</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>516</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>343289</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>343289</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>343289</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el/la adulto/a [KIDSCREEN 20] en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>94481</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>84429</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>104374</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>60,56%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>54,12%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>66,9%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>97415</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>88520</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>107053</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>85511</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>107080</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>62,64%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>56,92%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>68,84%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>94481</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>83968</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>104571</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>60,56%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>177560</t>
+          <t>177536</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>206161</t>
+          <t>205945</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,11%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>49425</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>40490</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>59045</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>31,68%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>25,95%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>37,85%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>50954</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>59781</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>41941</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>62461</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>32,77%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>26,56%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>38,44%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>49425</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>40226</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>59379</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>31,68%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>87153</t>
+          <t>86132</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>114315</t>
+          <t>114163</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,65%</t>
         </is>
       </c>
     </row>
@@ -3224,64 +3224,64 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7257</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3827</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12999</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4,65%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>8,33%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>6469</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2860</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11603</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3488</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>11688</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>4,16%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,46%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>7257</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>3497</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>12635</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>2,24%</t>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>8701</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21000</t>
+          <t>19884</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -3337,72 +3337,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2694</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>776</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7077</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,54%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>675</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2731</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3371</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2694</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6472</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8668</t>
+          <t>7581</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -3450,92 +3450,92 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2161</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5794</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>2161</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>678</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>5856</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>2161</t>
-        </is>
-      </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>680</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5724</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156017</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156017</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156017</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>156017</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>156017</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>156017</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>96927</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>85798</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>107547</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>55,33%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>48,98%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>61,39%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>92608</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>82040</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>102912</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>82376</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>103751</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>55,65%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>49,3%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>61,84%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>96927</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>85523</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>106543</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>55,33%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>175596</t>
+          <t>173453</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>204833</t>
+          <t>203512</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>59,58%</t>
         </is>
       </c>
     </row>
@@ -3793,72 +3793,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>59665</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>50592</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>71036</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>34,06%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>28,88%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>40,55%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>55931</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>46345</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>66171</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>45481</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>65840</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>33,61%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>27,85%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>39,77%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>59665</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>50152</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>69939</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>34,06%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>101281</t>
+          <t>102756</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>130021</t>
+          <t>131578</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,52%</t>
         </is>
       </c>
     </row>
@@ -3911,67 +3911,67 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>13160</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>8214</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>19623</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7,51%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>11,2%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>13418</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>8268</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>20088</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>8508</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>20245</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>8,06%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,97%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>12,07%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>13160</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>8518</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>19882</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>7,51%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19216</t>
+          <t>19569</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35359</t>
+          <t>35428</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -4019,72 +4019,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3657</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1273</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8673</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2504</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6704</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6434</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,5%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3657</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7968</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>2414</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12225</t>
+          <t>11109</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -4137,67 +4137,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>1778</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4247</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>1943</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5195</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5770</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,17%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1778</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>564</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4781</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7471</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>175187</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>175187</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>175187</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>166404</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>166404</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>166404</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>175187</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>175187</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>175187</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>191408</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>175847</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>206235</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>57,79%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>53,09%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>62,27%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>190024</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>174466</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>204506</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>174054</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>204083</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>59,03%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>54,2%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>63,53%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>191408</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>177438</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>206376</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>57,79%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>362196</t>
+          <t>360327</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>401932</t>
+          <t>402244</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,59%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>109090</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>95671</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>123921</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>32,94%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>28,89%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>37,42%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>106885</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>92885</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>122301</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>93821</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>121971</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>33,2%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>28,85%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>37,99%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>109090</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>94866</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>124125</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>32,94%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>196475</t>
+          <t>196594</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>233712</t>
+          <t>237320</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>36,34%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>20417</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>13238</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>27987</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>6,16%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>19887</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>13759</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>28272</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>13557</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>28557</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>6,18%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>4,27%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>8,78%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>20417</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>13402</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>28313</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>30710</t>
+          <t>30594</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>51591</t>
+          <t>50777</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -4701,72 +4701,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>6351</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3083</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>11438</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>3179</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1060</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>7634</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1056</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>7596</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,99%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>6351</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>3258</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>12275</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5256</t>
+          <t>5022</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16144</t>
+          <t>15675</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -4814,72 +4814,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3938</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1376</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>8587</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>1943</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5211</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5416</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,6%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>3938</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1304</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>8105</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10708</t>
+          <t>11065</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>331204</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>331204</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>331204</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>457</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>321919</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>321919</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>321919</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>482</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>331204</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>331204</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>331204</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el adulto en 2016 (tasa de respuesta: 98,52%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el/la adulto/a [KIDSCREEN 20] en 2016 (tasa de respuesta: 98,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>106343</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>94934</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>117358</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>57,42%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>51,26%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>63,37%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>105964</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>93753</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>116564</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>94380</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>117102</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>56,97%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>50,41%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>62,67%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>106343</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>96495</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>117728</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>57,42%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>195405</t>
+          <t>195220</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>228339</t>
+          <t>227391</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,26%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>63571</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>53586</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>74216</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>34,32%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>28,93%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>40,07%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>69021</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>58701</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>80974</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>58126</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>80440</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>37,11%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>31,56%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>43,54%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>63571</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>53479</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>73653</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>34,32%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117672</t>
+          <t>117692</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>149497</t>
+          <t>148233</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>39,93%</t>
         </is>
       </c>
     </row>
@@ -5505,67 +5505,67 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>10989</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6628</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17411</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>5,93%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>9,4%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>9787</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6042</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>16133</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>5595</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>15198</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>5,26%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,67%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>10989</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>6407</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>17308</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>5,93%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14493</t>
+          <t>14886</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29480</t>
+          <t>30038</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -5613,72 +5613,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1553</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4780</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>583</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2947</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3253</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1553</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4718</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>576</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5638</t>
+          <t>6211</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -5726,72 +5726,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2747</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6852</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>628</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3152</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3191</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2747</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>6253</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7490</t>
+          <t>7805</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>185204</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>185204</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>185204</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>267</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>185204</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>185204</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>185204</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,72 +5956,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>83072</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>72429</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>93663</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>47,91%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>41,77%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>54,02%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>82173</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>71355</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>92809</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>71289</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>92175</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>48,35%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>41,99%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>54,61%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>83072</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>72695</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>94815</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>47,91%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>148040</t>
+          <t>150576</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>179886</t>
+          <t>182577</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>53,18%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>67495</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>57144</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>78329</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>38,93%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>32,96%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>45,17%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>64718</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>55349</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>75640</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>54864</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>75576</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>38,08%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>32,57%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>44,51%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>67495</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>56312</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>78480</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>38,93%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>118141</t>
+          <t>116829</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>148941</t>
+          <t>146870</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>42,78%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18579</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12354</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>26169</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>10,71%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>7,12%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>15,09%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>21283</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>14517</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>29055</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>15438</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>29666</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>12,52%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>8,54%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>17,1%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>18579</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>12580</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>26031</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>10,71%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30546</t>
+          <t>30652</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>49568</t>
+          <t>50966</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -6295,72 +6295,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3525</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7681</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>778</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3933</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3881</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3525</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1371</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8307</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8659</t>
+          <t>9751</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -6413,102 +6413,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3981</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>993</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4974</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5046</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1718</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3681</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>5543</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1718</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>5865</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173396</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173396</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173396</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>169946</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>169946</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>169946</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173396</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173396</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173396</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>189416</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>173544</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>205271</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>52,82%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>48,39%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>57,24%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>267</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>188136</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>172687</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>204699</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>172613</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>203353</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>52,86%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>48,52%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>57,51%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>189416</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>173853</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>204992</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>52,82%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>354578</t>
+          <t>355292</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>402416</t>
+          <t>399331</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>55,89%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>131066</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>116917</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>147427</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36,55%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>32,6%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>41,11%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>133739</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>116979</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>148668</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>118331</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>148872</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>37,57%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>32,87%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>41,77%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>131066</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>116458</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>146823</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>36,55%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>244320</t>
+          <t>244565</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>288686</t>
+          <t>286233</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,06%</t>
         </is>
       </c>
     </row>
@@ -6864,72 +6864,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>29567</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>22261</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39555</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>8,25%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>6,21%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>11,03%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>31070</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>22959</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>39371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>23231</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>40715</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>8,73%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>6,45%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>11,06%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>29567</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>21012</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>38879</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>49835</t>
+          <t>49037</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>72745</t>
+          <t>72610</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -6977,72 +6977,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5078</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2217</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>10145</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,83%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>1361</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4887</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5395</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>5078</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>2167</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>10337</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>2941</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>12280</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -7090,72 +7090,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3473</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>1621</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5838</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5884</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>3473</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1366</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>7684</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10758</t>
+          <t>9875</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>358600</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>358600</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>358600</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>355928</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>355928</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>355928</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>492</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>358600</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>358600</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>358600</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
